--- a/astro-site/public/dl/kit-tareas-cafeteria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/03-tareas-manager.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Diario Manager'!$A$1:$G$34</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Semanal Manager'!$A$1:$G$32</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Mensual Manager'!$A$1:$G$32</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Handover Turno'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +85,11 @@
       <color rgb="00888888"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -142,50 +147,66 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -545,15 +566,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -561,6 +583,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -568,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -596,6 +620,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -603,8 +628,33 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -618,16 +668,16 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist Diario del Manager / Encargado</t>
@@ -641,10 +691,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -669,7 +720,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -686,10 +737,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -715,10 +764,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -744,10 +791,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -773,10 +818,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -802,10 +845,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -838,10 +879,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -867,10 +906,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -896,10 +933,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -925,10 +960,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -954,10 +987,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -983,10 +1014,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -1019,10 +1048,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -1048,10 +1075,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -1077,10 +1102,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -1106,10 +1129,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -1142,10 +1163,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>16</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -1171,10 +1190,8 @@
       <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -1200,10 +1217,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -1229,10 +1244,8 @@
       <c r="G26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="21" t="n">
+        <v>19</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
@@ -1258,10 +1271,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="20" t="n">
+        <v>20</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
@@ -1286,6 +1297,7 @@
       <c r="F28" s="11" t="n"/>
       <c r="G28" s="11" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="C30" s="16" t="inlineStr">
         <is>
@@ -1294,14 +1306,19 @@
       </c>
       <c r="D30" s="17">
         <f>COUNTIF(F5:F28,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>de 20</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F30">
+        <f>COUNTIF(B5:B28,"?*")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
@@ -1309,6 +1326,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
@@ -1327,8 +1345,18 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G28">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1342,16 +1370,16 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist Semanal del Manager (Lunes)</t>
@@ -1365,10 +1393,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1393,7 +1422,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1410,10 +1439,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -1439,10 +1466,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -1468,10 +1493,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -1497,10 +1520,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -1533,10 +1554,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -1562,10 +1581,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -1591,10 +1608,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -1620,10 +1635,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -1649,10 +1662,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -1678,10 +1689,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -1707,10 +1716,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -1743,10 +1750,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -1772,10 +1777,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -1801,10 +1804,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -1837,10 +1838,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -1866,10 +1865,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>16</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -1895,10 +1892,8 @@
       <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -1924,10 +1919,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -1952,6 +1945,7 @@
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="11" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="C28" s="16" t="inlineStr">
         <is>
@@ -1960,14 +1954,19 @@
       </c>
       <c r="D28" s="17">
         <f>COUNTIF(F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>de 18</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -1975,6 +1974,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
@@ -1987,14 +1987,24 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F17 F19 F20 F21 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2008,16 +2018,16 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist Mensual del Manager</t>
@@ -2031,10 +2041,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2059,7 +2070,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2076,10 +2087,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -2105,10 +2114,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -2134,10 +2141,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -2163,10 +2168,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2192,10 +2195,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -2228,10 +2229,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -2257,10 +2256,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -2286,10 +2283,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -2322,10 +2317,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -2351,10 +2344,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -2380,10 +2371,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -2409,10 +2398,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -2438,10 +2425,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -2467,10 +2452,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -2503,10 +2486,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -2532,10 +2513,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>16</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -2561,10 +2540,8 @@
       <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -2590,10 +2567,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -2618,6 +2593,7 @@
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="11" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="C28" s="16" t="inlineStr">
         <is>
@@ -2626,14 +2602,19 @@
       </c>
       <c r="D28" s="17">
         <f>COUNTIF(F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>de 18</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -2641,6 +2622,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
@@ -2659,8 +2641,18 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F16 F17 F18 F19 F20 F21 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2674,16 +2666,16 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Checklist de Cambio de Turno (Handover)</t>
@@ -2697,10 +2689,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2725,7 +2718,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2742,10 +2735,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -2771,10 +2762,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -2800,10 +2789,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -2836,10 +2823,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -2865,10 +2850,8 @@
       <c r="G10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -2894,10 +2877,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -2930,10 +2911,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -2959,10 +2938,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2988,10 +2965,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -3017,10 +2992,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -3046,10 +3019,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -3074,6 +3045,7 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="C20" s="16" t="inlineStr">
         <is>
@@ -3082,14 +3054,19 @@
       </c>
       <c r="D20" s="17">
         <f>COUNTIF(F5:F18,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>de 11</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F20">
+        <f>COUNTIF(B5:B18,"?*")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
@@ -3097,6 +3074,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
@@ -3114,7 +3092,17 @@
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/03-tareas-manager.xlsx
@@ -14,9 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Handover Turno'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -663,7 +667,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1355,8 +1359,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1365,7 +1377,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2003,8 +2015,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2013,7 +2033,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2651,8 +2671,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2661,7 +2689,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3102,7 +3130,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/03-tareas-manager.xlsx
@@ -14,14 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Handover Turno'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,8 +95,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -126,6 +141,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -153,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,6 +215,50 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -572,79 +636,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Tareas del Manager / Encargado — Cafetería / Brunch</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Checklists para la gestión diaria, semanal y mensual de tu cafetería.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• El checklist diario se completa cada día</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• El semanal se revisa cada lunes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>• El mensual se revisa el primer día de cada mes</t>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>• El handover se usa en cada cambio de turno</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="B9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = tarea pendiente · ✓ = completada (escribe en columna 'Hecha')</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
         </is>
       </c>
     </row>
     <row r="14"/>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra café).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>▸ Estás en 03-tareas-manager.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -669,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -719,7 +871,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -734,628 +886,726 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANTES DE ABRIR</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Revisar email y mensajes pendientes</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Revisar reservas del día (brunch fin de semana)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Comprobar que todo el equipo ha llegado</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Briefing rápido: especiales del día, alérgenos, VIPs</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Verificar stock crítico: café, leche, pan, bollería</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE EL SERVICIO</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Supervisar tiempos de espera en barra y cocina</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Gestionar reservas que llegan / walk-ins</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Resolver incidencias con clientes</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Controlar calidad de bebidas y platos en pase</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Apoyar en barra/sala si hay pico de trabajo</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Supervisar limpieza de mesas entre clientes</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  GESTIÓN Y ADMINISTRACIÓN</t>
         </is>
       </c>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="26" t="n"/>
+      <c r="G18" s="26" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Revisar redes sociales: responder comentarios y mensajes</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Hacer foto del plato/bebida del día para RRSS</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Gestionar pedidos a proveedores para mañana</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Revisar ventas del día hasta el momento</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  AL CERRAR</t>
         </is>
       </c>
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="26" t="n"/>
+      <c r="G23" s="26" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Supervisar cierre de cocina, sala y barra</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>Cuadrar caja y anotar incidencias</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Preparar briefing para el turno de mañana</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n">
+      <c r="A27" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Revisar planificación de personal para mañana</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="n">
+      <c r="A28" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>Cerrar y validar el registro diario de jornada del equipo (entradas, salidas y pausas)</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>Cerrar local: alarma, luces, gas, puertas</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-    </row>
-    <row r="29"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
     <row r="30">
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D30" s="17">
-        <f>COUNTIF(F5:F28,"✓")</f>
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="30" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="30" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="30" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D36" s="17">
+        <f>COUNTIFS(B5:B34,"?*",F5:F34,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F30">
-        <f>COUNTIF(B5:B28,"?*")</f>
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="F36">
+        <f>COUNTIF(B5:B34,"?*")-COUNTIF(F5:F34,"N/A")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A36:C36"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G28">
+  <conditionalFormatting sqref="A5:G34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1379,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1651,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1679,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1444,574 +1694,645 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANÁLISIS</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Revisar ventas de la semana anterior</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Analizar productos más vendidos y menos vendidos</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Revisar feedback de clientes (Google, TripAdvisor, RRSS)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Evaluar desperdicio/merma de la semana</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  PEDIDOS Y STOCK</t>
         </is>
       </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Hacer pedido semanal de café (variedades)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Hacer pedido semanal de leches (entera, vegetales)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Hacer pedido de bollería/pastelería si es externa</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Hacer pedido de frescos: fruta, verdura, lácteos</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Verificar stock de productos de limpieza</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Verificar stock de packaging: vasos, tapas, bolsas</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Verificar stock suficiente para fin de semana</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPO Y FORMACIÓN</t>
         </is>
       </c>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="26" t="n"/>
+      <c r="G18" s="26" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Revisar horarios del personal para la semana</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Reunión rápida de equipo (10 min): objetivos semana</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Identificar necesidad de refuerzo fin de semana</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MANTENIMIENTO Y LIMPIEZA</t>
         </is>
       </c>
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="26" t="n"/>
+      <c r="G22" s="26" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Supervisar limpieza profunda semanal</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Verificar estado de máquina espresso</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>Revisar estado de mobiliario (sillas, mesas, terraza)</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Verificar caducidades en almacén y cámaras</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-    </row>
-    <row r="27"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
     <row r="28">
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D28" s="17">
-        <f>COUNTIF(F5:F26,"✓")</f>
+      <c r="A28" s="33" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D33" s="17">
+        <f>COUNTIFS(B5:B31,"?*",F5:F31,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28">
-        <f>COUNTIF(B5:B26,"?*")</f>
+      <c r="F33">
+        <f>COUNTIF(B5:B31,"?*")-COUNTIF(F5:F31,"N/A")</f>
         <v>18.0</v>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G26">
+  <conditionalFormatting sqref="A5:G31">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F17 F19 F20 F21 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F17 F19 F20 F21 F23 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2035,7 +2356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2057,7 +2378,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2406,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2100,574 +2421,672 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  FINANCIERO</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Revisar P&amp;L del mes (ingresos vs gastos)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Calcular food cost del mes</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Revisar coste laboral vs facturación</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Negociar precios con proveedores si aplica</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Revisar tarifas de delivery (Glovo, Uber Eats)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPO</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Evaluación rápida de desempeño del equipo</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Revisar necesidades de formación (latte art, atención)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Actualizar cuadrante de vacaciones</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del mes (hay que conservarlos 4 años)</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MANTENIMIENTO</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="26" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Descalcificar máquina de espresso</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Técnico/Barista</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>Revisar molinillo: muelas, calibración</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Técnico/Barista</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Mantenimiento horno: resistencias, puerta, juntas</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Revisar lavavajillas: filtros, abrillantador, sal</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>Revisar climatización: filtros, temperatura</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Verificar botiquín: stock completo, caducidades</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MARKETING Y CARTA</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="26" t="n"/>
+      <c r="G23" s="26" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Evaluar carta: rotar platos estacionales</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Planificar especiales del mes siguiente</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Revisar fotos de RRSS: calidad, frecuencia</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>Evaluar valoraciones online y responder reseñas pendientes</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-    </row>
-    <row r="27"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
     <row r="28">
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D28" s="17">
-        <f>COUNTIF(F5:F26,"✓")</f>
+      <c r="A28" s="33" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="30" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D34" s="17">
+        <f>COUNTIFS(B5:B32,"?*",F5:F32,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28">
-        <f>COUNTIF(B5:B26,"?*")</f>
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="F34">
+        <f>COUNTIF(B5:B32,"?*")-COUNTIF(F5:F32,"N/A")</f>
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A23:G23"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G26">
+  <conditionalFormatting sqref="A5:G32">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F16 F17 F18 F19 F20 F21 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21 F22 F24 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2691,7 +3110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2741,7 +3160,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2756,377 +3175,442 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ESTADO DEL SERVICIO</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Mesas ocupadas y reservas pendientes</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Comandas en curso en cocina</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Bebidas pendientes en barra</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  INCIDENCIAS</t>
         </is>
       </c>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="26" t="n"/>
+      <c r="G9" s="26" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Incidencias del turno que sale</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Quejas o peticiones especiales de clientes</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Pedidos pendientes de recibir</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  STOCK Y EQUIPOS</t>
         </is>
       </c>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Estado del stock de café en grano</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Stock de leches (qué queda y qué falta)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Stock de bollería en vitrina</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Estado de la máquina de espresso (algún problema)</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Estado de limpieza general</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Turno saliente</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-    </row>
-    <row r="19"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
     <row r="20">
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D20" s="17">
-        <f>COUNTIF(F5:F18,"✓")</f>
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D25" s="17">
+        <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F20">
-        <f>COUNTIF(B5:B18,"?*")</f>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
         <v>11.0</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G18">
+  <conditionalFormatting sqref="A5:G23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
